--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="15" windowWidth="19200" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="player" sheetId="1" r:id="rId1"/>
-    <sheet name="brooklyn" sheetId="4" r:id="rId2"/>
-    <sheet name="rogues" sheetId="5" r:id="rId3"/>
-    <sheet name="monsters" sheetId="2" r:id="rId4"/>
-    <sheet name="animals" sheetId="6" r:id="rId5"/>
+    <sheet sheetId="1" name="player" state="visible" r:id="rId4"/>
+    <sheet sheetId="4" name="brooklyn" state="visible" r:id="rId5"/>
+    <sheet sheetId="5" name="rogues" state="visible" r:id="rId6"/>
+    <sheet sheetId="2" name="monsters" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="animals" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -41,7 +41,7 @@
     <t>_view</t>
   </si>
   <si>
-    <t>"faceR":true,
+    <t xml:space="preserve">"faceR":true,
 "anchor":{"x":0,"y":16}, 
 "w":32, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -52,7 +52,7 @@
     <t>_shape</t>
   </si>
   <si>
-    <t>"body":{"sprite":"body-man","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"body-man","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "head":{"sprite":"head-wick","scale":0.25,"y":3.5},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
@@ -118,39 +118,39 @@
     <t>"job":"trader","gold":200,"style":"weak","trade":true</t>
   </si>
   <si>
-    <t>"job":"butcher","gold":200,
+    <t xml:space="preserve">"job":"butcher","gold":200,
 "abilities":["fireball","heal"],"meat":"raw_meat","trade":true</t>
   </si>
   <si>
     <t>"job":"merchant","gold":200,"trade":true</t>
   </si>
   <si>
-    <t>"body":{"sprite":"trump","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"trump","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"melanie","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"melanie","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"musk","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"musk","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"xi","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"xi","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"macron","scale":0.25,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"macron","scale":0.25,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"storage":{"capacity":-1,
+    <t xml:space="preserve">"storage":{"capacity":-1,
 "items":["sword_01",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
-    <t>"storage":{"capacity":-1,
+    <t xml:space="preserve">"storage":{"capacity":-1,
 "items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
@@ -388,23 +388,42 @@
     <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/macron-home"</t>
   </si>
   <si>
+    <t>rogue-1</t>
+  </si>
+  <si>
+    <t>rogue-2</t>
+  </si>
+  <si>
     <t>"job":"rogue","gold":200,"type":"enemy"</t>
   </si>
   <si>
+    <t xml:space="preserve">"body":{"sprite":"rogue","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32},
+"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+  </si>
+  <si>
     <t>"equips":["sword_01"]</t>
   </si>
   <si>
+    <t>"equips":["bow_01"]</t>
+  </si>
+  <si>
     <t>attrs</t>
   </si>
   <si>
-    <t>"attack": 5,
-"defense": 0</t>
+    <t xml:space="preserve">"atk": 5,
+"def": 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"atk": 5,
+"def": 0,
+"resists":{"fire_res":0.5}</t>
   </si>
   <si>
     <t>states</t>
   </si>
   <si>
-    <t>"life": {"cur":50,"max":50},
+    <t xml:space="preserve">"life": {"cur":50,"max":50},
 "hunger": {"cur":0,"max":100},
 "thirst": {"cur":0,"max":100}</t>
   </si>
@@ -415,7 +434,7 @@
     <t>monsters:0</t>
   </si>
   <si>
-    <t>"faceR":false,
+    <t xml:space="preserve">"faceR":false,
 "anchor":{"x":-16,"y":16}, 
 "w":64, "h":64,
 "b":{"l":0,"r":0,"t":32,"b":0},
@@ -423,7 +442,7 @@
 "z":{"l":0,"r":0,"t":32,"b":0}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"monsters:0","scale":2,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"monsters:0","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
@@ -445,60 +464,35 @@
     <t>"meat":"raw_meat","style":"skittish"</t>
   </si>
   <si>
-    <t>"body":{"sprite":"animals:42","scale":2,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"animals:42","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
   </si>
   <si>
-    <t>"body":{"sprite":"animals:82","scale":2,"y":32},
+    <t xml:space="preserve">"body":{"sprite":"animals:82","scale":2,"y":32},
 "corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
-  </si>
-  <si>
-    <t>"body":{"sprite":"rogue","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rogue-1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>rogue-2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>"equips":["bow_01"]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="164" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="136"/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="微軟正黑體 Light"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="新細明體"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -529,12 +523,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -833,17 +827,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="52.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="1"/>
+    <col min="3" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -851,7 +844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -859,7 +852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -867,7 +860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="94.5" customHeight="1">
+    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,7 +868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="63" customHeight="1">
+    <row r="5" ht="63" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -883,7 +876,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -891,7 +884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -899,23 +892,99 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="63" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="66" style="1" customWidth="1"/>
@@ -924,11 +993,10 @@
     <col min="5" max="5" width="75" style="1" customWidth="1"/>
     <col min="6" max="6" width="67.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="70.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="1"/>
+    <col min="8" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -951,7 +1019,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -974,7 +1042,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.5" customHeight="1">
+    <row r="3" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -997,7 +1065,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="94.5" customHeight="1">
+    <row r="4" ht="94.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1020,7 +1088,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="47.25" customHeight="1">
+    <row r="5" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1043,7 +1111,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="31.5" customHeight="1">
+    <row r="6" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -1063,7 +1131,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1086,7 +1154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1109,7 +1177,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1132,7 +1200,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -1155,7 +1223,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1178,7 +1246,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1201,7 +1269,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1224,7 +1292,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,7 +1312,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1264,7 +1332,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1281,7 +1349,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1298,7 +1366,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
@@ -1315,7 +1383,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1332,7 +1400,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1349,7 +1417,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
@@ -1366,7 +1434,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>14</v>
       </c>
@@ -1383,7 +1451,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
@@ -1401,34 +1469,33 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="56.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="54.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1439,18 +1506,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1">
+    <row r="3" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="94.5" customHeight="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1461,228 +1528,149 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="47.25" customHeight="1">
+    <row r="5" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="31.5" customHeight="1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="47.25" customHeight="1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="63" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="94.5" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="31.5" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="47.25" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="200" verticalDpi="200"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
     <col min="2" max="3" width="63" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="94.5" customHeight="1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="31.5" customHeight="1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="31.5" customHeight="1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="47.25" customHeight="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1690,7 +1678,6 @@
       <c r="C8" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -54,8 +54,7 @@
   <si>
     <t xml:space="preserve">"body":{"sprite":"body-man","scale":0.25,"y":32},
 "hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"head":{"sprite":"head-wick","scale":0.25,"y":3.5},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+"head":{"sprite":"head-wick","scale":0.25,"y":3.5}</t>
   </si>
   <si>
     <t>inv</t>
@@ -125,25 +124,20 @@
     <t>"job":"merchant","gold":200,"trade":true</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"trump","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"body":{"sprite":"melanie","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <t>"body":{"sprite":"trump","scale":0.25,"y":32}</t>
+  </si>
+  <si>
+    <t>"body":{"sprite":"melanie","scale":0.25,"y":32}</t>
   </si>
   <si>
     <t xml:space="preserve">"body":{"sprite":"musk","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"body":{"sprite":"xi","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"body":{"sprite":"macron","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+"hand":{"sprite":"hand-man","scale":0.25,"y":32}</t>
+  </si>
+  <si>
+    <t>"body":{"sprite":"xi","scale":0.25,"y":32}</t>
+  </si>
+  <si>
+    <t>"body":{"sprite":"macron","scale":0.25,"y":32}</t>
   </si>
   <si>
     <t xml:space="preserve">"storage":{"capacity":-1,
@@ -398,8 +392,7 @@
   </si>
   <si>
     <t xml:space="preserve">"body":{"sprite":"rogue","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+"hand":{"sprite":"hand-man","scale":0.25,"y":32}</t>
   </si>
   <si>
     <t>"equips":["sword_01"]</t>
@@ -442,8 +435,7 @@
 "z":{"l":0,"r":0,"t":32,"b":0}</t>
   </si>
   <si>
-    <t xml:space="preserve">"body":{"sprite":"monsters:0","scale":2,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+    <t>"body":{"sprite":"monsters:0","scale":2,"y":32}</t>
   </si>
   <si>
     <t>wolf</t>
@@ -465,11 +457,11 @@
   </si>
   <si>
     <t xml:space="preserve">"body":{"sprite":"animals:42","scale":2,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+"fall":180</t>
   </si>
   <si>
     <t xml:space="preserve">"body":{"sprite":"animals:82","scale":2,"y":32},
-"corpse":{"sprite":"rip","scale":0.5,"y":32}</t>
+"fall":180</t>
   </si>
 </sst>
 </file>

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -12,13 +12,14 @@
     <sheet sheetId="5" name="rogues" state="visible" r:id="rId6"/>
     <sheet sheetId="2" name="monsters" state="visible" r:id="rId7"/>
     <sheet sheetId="6" name="animals" state="visible" r:id="rId8"/>
+    <sheet sheetId="3" name="props" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="145">
   <si>
     <t>id</t>
   </si>
@@ -141,6 +142,10 @@
   </si>
   <si>
     <t xml:space="preserve">"storage":{"capacity":-1,
+"items":["sword_01",{"id":"helmet_01","count":1},"dummy"]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"storage":{"capacity":-1,
 "items":["sword_01",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
@@ -462,6 +467,20 @@
   <si>
     <t xml:space="preserve">"body":{"sprite":"animals:82","scale":2,"y":32},
 "fall":180</t>
+  </si>
+  <si>
+    <t>dummy</t>
+  </si>
+  <si>
+    <t>rogue</t>
+  </si>
+  <si>
+    <t>"body":{"sprite":"rogue","scale":0.25,"y":32}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"hpMax": 500,
+"def": 0,
+"eva": 0</t>
   </si>
 </sst>
 </file>
@@ -910,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -918,7 +937,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -926,7 +945,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -934,7 +953,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -942,23 +961,23 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -970,6 +989,67 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="63" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -1111,16 +1191,16 @@
         <v>37</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1151,22 +1231,22 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1174,22 +1254,22 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1197,22 +1277,22 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1220,22 +1300,22 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1243,22 +1323,22 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1266,22 +1346,22 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1289,19 +1369,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1309,19 +1389,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1329,16 +1409,16 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1346,16 +1426,16 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1363,16 +1443,16 @@
         <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1380,16 +1460,16 @@
         <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1397,16 +1477,16 @@
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1414,16 +1494,16 @@
         <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1431,16 +1511,16 @@
         <v>14</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1448,16 +1528,16 @@
         <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1481,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1503,10 +1583,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1525,10 +1605,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1536,32 +1616,32 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1590,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1601,10 +1681,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1612,10 +1692,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1623,10 +1703,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1634,32 +1714,32 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -142,7 +142,7 @@
   </si>
   <si>
     <t xml:space="preserve">"storage":{"capacity":-1,
-"items":["sword_01",{"id":"helmet_01","count":1},"dummy"]}</t>
+"items":["sword_01",{"id":"helmet_01","count":1},"dummy","dummy","dummy"]}</t>
   </si>
   <si>
     <t xml:space="preserve">"storage":{"capacity":-1,
@@ -1049,7 +1049,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>id</t>
   </si>
@@ -153,238 +153,79 @@
 "items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
-    <t>"t":"06:00~06:10", "p":"bed~stair-dn", "map":"m_04x05/trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"06:10~06:20", "p":"trump-p1~stair-up", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/musk-home"</t>
-  </si>
-  <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/karen-home"</t>
-  </si>
-  <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/xi-home"</t>
-  </si>
-  <si>
-    <t>"t":"07:40~07:50", "p":"bed~door", "map":"m_04x05/macron-home"</t>
-  </si>
-  <si>
-    <t>"t":"06:10~06:20", "p":"stair-up~trump-p1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"06:20~06:30", "p":"stair-dn~bed", "map":"m_04x05/trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"07:50~08:00", "p":"musk-home~musk-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"07:50~08:00", "p":"karen-home~karen-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"07:50~08:00", "p":"xi-home~xi-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"07:50~08:00", "p":"macron-home~macron-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"06:20~22:30", "p":"trump-p1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"06:30~14:30", "p":"bed", "map":"m_04x05/trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"08:00~11:50", "p":"musk-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"08:00~11:50", "p":"karen-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"08:00~11:50", "p":"xi-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"08:00~11:50", "p":"macron-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"22:30~22:40", "p":"trump-p1~stair-up", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"14:30~14:40", "p":"bed~stair-dn", "map":"m_04x05/trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"11:50~12:00", "p":"musk-p1~trump-inn", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"11:50~12:00", "p":"karen-p1~trump-inn", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"11:50~12:00", "p":"xi-p1~trump-inn", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"11:50~12:00", "p":"macron-p1~trump-inn", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"22:40~22:50", "p":"stair-dn~bed", "map":"m_04x05/trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"14:40~14:50", "p":"stair-up~melanie-p1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:00~12:10", "p":"door~sit-1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:00~12:10", "p":"door~sit-3", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:00~12:10", "p":"door~sit-5", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:00~12:10", "p":"door~sit-7", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"22:50~06:00", "p":"bed", "map":"m_04x05/trump-inn-f2"</t>
-  </si>
-  <si>
-    <t>"t":"14:50~22:30", "p":"melanie-p1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:10~13:00", "p":"sit-1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:10~13:00", "p":"sit-3", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:10~13:00", "p":"sit-5", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"12:10~13:00", "p":"sit-7", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"22:30~22:40", "p":"melanie-p1~trump-p1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:00~13:10", "p":"sit-1~door", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:00~13:10", "p":"sit-3~door", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:00~13:10", "p":"sit-5~door", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:00~13:10", "p":"sit-7~door", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"22:40~06:10", "p":"trump-p1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"13:10~13:20", "p":"trump-inn~musk-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"13:10~13:20", "p":"trump-inn~karen-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"13:10~13:20", "p":"trump-inn~xi-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"13:10~13:20", "p":"trump-inn~macron-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"13:20~17:00", "p":"musk-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"13:20~17:00", "p":"karen-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"13:20~17:00", "p":"xi-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"13:20~17:00", "p":"macron-p1", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"17:00~17:10", "p":"musk-p1~trump-inn", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"17:00~17:10", "p":"karen-p1~trump-inn", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"17:00~17:10", "p":"xi-p1~trump-inn", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"17:00~17:10", "p":"macron-p1~trump-inn", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"17:10~17:20", "p":"door~sit-1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:10~17:20", "p":"door~sit-3", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:10~17:20", "p":"door~sit-5", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:10~17:20", "p":"door~sit-7", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:20~20:00", "p":"sit-1", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:20~20:00", "p":"sit-3", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:20~20:00", "p":"sit-5", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"17:20~20:00", "p":"sit-7", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:00~20:10", "p":"sit-1~door", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:00~20:10", "p":"sit-3~door", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:00~20:10", "p":"sit-5~door", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:00~20:10", "p":"sit-7~door", "map":"m_04x05/trump-inn-f1"</t>
-  </si>
-  <si>
-    <t>"t":"20:10~20:20", "p":"trump-inn~musk-home", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"20:10~20:20", "p":"trump-inn~karen-home", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"20:10~20:20", "p":"trump-inn~xi-home", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"20:10~20:20", "p":"trump-inn~macron-home", "map":"m/m_04x05"</t>
-  </si>
-  <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/musk-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/karen-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/xi-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:20~20:30", "p":"door~bed", "map":"m_04x05/macron-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/musk-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/karen-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/xi-home"</t>
-  </si>
-  <si>
-    <t>"t":"20:30~07:40", "p":"bed", "map":"m_04x05/macron-home"</t>
+    <t>"t":"@06:20", "go":"trump-p1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@06:30", "go":"bed", "map":"m_04x05/trump-inn-f2"</t>
+  </si>
+  <si>
+    <t>"t":"@08:00", "go":"musk-p1", "map":"m/m_04x05"</t>
+  </si>
+  <si>
+    <t>"t":"@08:00", "go":"karen-p1", "map":"m/m_04x05"</t>
+  </si>
+  <si>
+    <t>"t":"@08:00", "go":"xi-p1", "map":"m/m_04x05"</t>
+  </si>
+  <si>
+    <t>"t":"@08:00", "go":"macron-p1", "map":"m/m_04x05"</t>
+  </si>
+  <si>
+    <t>"t":"@22:50", "go":"bed", "map":"m_04x05/trump-inn-f2"</t>
+  </si>
+  <si>
+    <t>"t":"@14:50", "go":"melanie-p1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@12:10", "go":"sit-1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@12:10", "go":"sit-3", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@12:10", "go":"sit-5", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@12:10", "go":"sit-7", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@22:40", "go":"trump-p1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@13:20", "go":"musk-p1", "map":"m/m_04x05"</t>
+  </si>
+  <si>
+    <t>"t":"@13:20", "go":"karen-p1", "map":"m/m_04x05"</t>
+  </si>
+  <si>
+    <t>"t":"@13:20", "go":"xi-p1", "map":"m/m_04x05"</t>
+  </si>
+  <si>
+    <t>"t":"@13:20", "go":"macron-p1", "map":"m/m_04x05"</t>
+  </si>
+  <si>
+    <t>"t":"@17:20", "go":"sit-1", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@17:20", "go":"sit-3", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@17:20", "go":"sit-5", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@17:20", "go":"sit-7", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"@20:30", "go":"bed", "map":"m_04x05/musk-home"</t>
+  </si>
+  <si>
+    <t>"t":"@20:30", "go":"bed", "map":"m_04x05/karen-home"</t>
+  </si>
+  <si>
+    <t>"t":"@20:30", "go":"bed", "map":"m_04x05/xi-home"</t>
+  </si>
+  <si>
+    <t>"t":"@20:30", "go":"bed", "map":"m_04x05/macron-home"</t>
   </si>
   <si>
     <t>rogue-1</t>
@@ -929,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -937,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -945,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -953,7 +794,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -961,23 +802,23 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1006,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1014,7 +855,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1036,15 +877,15 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1276,269 +1117,181 @@
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>93</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>105</v>
-      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>109</v>
-      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>113</v>
-      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>117</v>
-      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1561,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1583,10 +1336,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1605,10 +1358,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1616,35 +1369,35 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1670,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1681,10 +1434,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1692,10 +1445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1703,10 +1456,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1714,32 +1467,32 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="104">
   <si>
     <t>id</t>
   </si>
@@ -91,6 +91,12 @@
     <t>macron</t>
   </si>
   <si>
+    <t>guard-1</t>
+  </si>
+  <si>
+    <t>guard-2</t>
+  </si>
+  <si>
     <t>head-trump</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
     <t>"job":"merchant","gold":200,"trade":true</t>
   </si>
   <si>
+    <t>"job":"guard","gold":50,"style":"passive_fighter"</t>
+  </si>
+  <si>
     <t>"body":{"sprite":"trump","scale":0.25,"y":32}</t>
   </si>
   <si>
@@ -141,6 +150,10 @@
     <t>"body":{"sprite":"macron","scale":0.25,"y":32}</t>
   </si>
   <si>
+    <t xml:space="preserve">"body":{"sprite":"rogue","scale":0.25,"y":32},
+"hand":{"sprite":"hand-man","scale":0.25,"y":32}</t>
+  </si>
+  <si>
     <t xml:space="preserve">"storage":{"capacity":-1,
 "items":["sword_01",{"id":"helmet_01","count":1},"dummy","dummy","dummy"]}</t>
   </si>
@@ -153,6 +166,9 @@
 "items":["sword_01","chest_01","gloves_01","chest_02",{"id":"helmet_01","count":1}]}</t>
   </si>
   <si>
+    <t>"equips":["sword_01","helmet_01","chest_01"]</t>
+  </si>
+  <si>
     <t>"t":"@06:20", "go":"trump-p1", "map":"m_04x05/trump-inn-f1"</t>
   </si>
   <si>
@@ -171,6 +187,12 @@
     <t>"t":"@08:00", "go":"macron-p1", "map":"m/m_04x05"</t>
   </si>
   <si>
+    <t>"t":"@08:00", "go":"guard-p1", "map":"m/m_04x05", "do":"patrol", "route":["guard-p1","guard-p2","guard-p3","guard-p2","guard-p4"], "wait":3</t>
+  </si>
+  <si>
+    <t>"t":"@20:00", "go":"guard-p1", "map":"m/m_04x05", "do":"patrol", "route":["guard-p1","guard-p2","guard-p3","guard-p2","guard-p4"], "wait":3</t>
+  </si>
+  <si>
     <t>"t":"@22:50", "go":"bed", "map":"m_04x05/trump-inn-f2"</t>
   </si>
   <si>
@@ -189,6 +211,12 @@
     <t>"t":"@12:10", "go":"sit-7", "map":"m_04x05/trump-inn-f1"</t>
   </si>
   <si>
+    <t>"t":"20:00", "go":"sit-2", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
+    <t>"t":"08:00", "go":"sit-4", "map":"m_04x05/trump-inn-f1"</t>
+  </si>
+  <si>
     <t>"t":"@22:40", "go":"trump-p1", "map":"m_04x05/trump-inn-f1"</t>
   </si>
   <si>
@@ -204,6 +232,12 @@
     <t>"t":"@13:20", "go":"macron-p1", "map":"m/m_04x05"</t>
   </si>
   <si>
+    <t>"t":"21:02", "go":"bed", "map":"m_04x05/house-08"</t>
+  </si>
+  <si>
+    <t>"t":"09:07", "go":"bed", "map":"m_04x05/house-08"</t>
+  </si>
+  <si>
     <t>"t":"@17:20", "go":"sit-1", "map":"m_04x05/trump-inn-f1"</t>
   </si>
   <si>
@@ -216,6 +250,12 @@
     <t>"t":"@17:20", "go":"sit-7", "map":"m_04x05/trump-inn-f1"</t>
   </si>
   <si>
+    <t>"t":"05:41", "go":"guard-room-p1", "map":"m_04x05/house-08", "do":"idle"</t>
+  </si>
+  <si>
+    <t>"t":"17:51", "go":"guard-room-p1", "map":"m_04x05/house-08", "do":"idle"</t>
+  </si>
+  <si>
     <t>"t":"@20:30", "go":"bed", "map":"m_04x05/musk-home"</t>
   </si>
   <si>
@@ -235,10 +275,6 @@
   </si>
   <si>
     <t>"job":"rogue","gold":200,"type":"enemy"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"body":{"sprite":"rogue","scale":0.25,"y":32},
-"hand":{"sprite":"hand-man","scale":0.25,"y":32}</t>
   </si>
   <si>
     <t>"equips":["sword_01"]</t>
@@ -770,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -778,7 +814,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -786,7 +822,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -794,7 +830,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -802,23 +838,23 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -847,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -855,7 +891,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -877,15 +913,15 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="47.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -896,7 +932,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.85546875" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="1" customWidth="1"/>
@@ -905,11 +941,11 @@
     <col min="4" max="4" width="76" style="1" customWidth="1"/>
     <col min="5" max="5" width="75" style="1" customWidth="1"/>
     <col min="6" max="6" width="67.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="70.5703125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="1" customWidth="1"/>
+    <col min="7" max="9" width="70.5703125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -931,54 +967,72 @@
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,51 +1054,69 @@
       <c r="G4" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="47.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" ht="31.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -1066,113 +1138,145 @@
       <c r="G7" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1182,8 +1286,10 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
@@ -1193,8 +1299,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -1204,8 +1312,10 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1215,8 +1325,10 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1226,8 +1338,10 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
@@ -1237,8 +1351,10 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1248,8 +1364,10 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1259,8 +1377,10 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
@@ -1270,8 +1390,10 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>14</v>
       </c>
@@ -1281,8 +1403,10 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>14</v>
       </c>
@@ -1292,6 +1416,8 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1314,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1325,10 +1451,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1336,10 +1462,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1358,10 +1484,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1369,35 +1495,35 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1423,10 +1549,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1434,10 +1560,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1445,10 +1571,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="94.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1456,10 +1582,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1467,32 +1593,32 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" ht="47.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -332,10 +332,10 @@
     <t>animals:82</t>
   </si>
   <si>
-    <t>"meat":"raw_meat","skin":"plet","style":"aggressive"</t>
-  </si>
-  <si>
-    <t>"meat":"raw_meat","style":"skittish"</t>
+    <t>"meat":"raw_meat","skin":"plet","style":"aggressive","animal":true</t>
+  </si>
+  <si>
+    <t>"meat":"raw_meat","style":"skittish","animal":true</t>
   </si>
   <si>
     <t xml:space="preserve">"body":{"sprite":"animals:42","scale":2,"y":32},

--- a/xls/role.xlsx
+++ b/xls/role.xlsx
@@ -112,26 +112,26 @@
     <t>head-macron</t>
   </si>
   <si>
-    <t>"job":"innkeeper","gold":200,"trade":true</t>
-  </si>
-  <si>
-    <t>"job":"innkeeper","gold":200,"style":"passive_coward","trade":true</t>
-  </si>
-  <si>
-    <t>"job":"smith","gold":200,"weapon":"sword_01","trade":true</t>
-  </si>
-  <si>
-    <t>"job":"trader","gold":200,"style":"weak","trade":true</t>
+    <t>"job":"innkeeper","gold":200,"trade":true,"unique":true</t>
+  </si>
+  <si>
+    <t>"job":"innkeeper","gold":200,"style":"passive_coward","trade":true,"unique":true</t>
+  </si>
+  <si>
+    <t>"job":"smith","gold":200,"weapon":"sword_01","trade":true,"unique":true</t>
+  </si>
+  <si>
+    <t>"job":"trader","gold":200,"style":"weak","trade":true,"unique":true</t>
   </si>
   <si>
     <t xml:space="preserve">"job":"butcher","gold":200,
-"abilities":["fireball","heal"],"meat":"raw_meat","trade":true</t>
-  </si>
-  <si>
-    <t>"job":"merchant","gold":200,"trade":true</t>
-  </si>
-  <si>
-    <t>"job":"guard","gold":50,"style":"passive_fighter"</t>
+"abilities":["fireball","heal"],"meat":"raw_meat","trade":true,"unique":true</t>
+  </si>
+  <si>
+    <t>"job":"merchant","gold":200,"trade":true,"unique":true</t>
+  </si>
+  <si>
+    <t>"job":"guard","gold":50,"style":"passive_fighter","unique":true</t>
   </si>
   <si>
     <t>"body":{"sprite":"trump","scale":0.25,"y":32}</t>
